--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -39,27 +39,27 @@
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile Chico</t>
+  </si>
+  <si>
     <t xml:space="preserve">O'Higgins</t>
   </si>
   <si>
-    <t xml:space="preserve">Cochrane</t>
+    <t xml:space="preserve">Coyhaique</t>
   </si>
   <si>
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">Chile Chico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Guaitecas</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20.12</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="3">
@@ -519,13 +519,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11302</v>
+        <v>11301</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.6</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="4">
@@ -536,13 +536,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11301</v>
+        <v>11303</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.35</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="5">
@@ -550,16 +550,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11102</v>
+        <v>11201</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="6">
@@ -567,16 +567,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11401</v>
+        <v>11202</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.61</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="7">
@@ -584,16 +584,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11303</v>
+        <v>11401</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.4</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="8">
@@ -601,16 +601,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11202</v>
+        <v>11302</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.16</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="9">
@@ -618,16 +618,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>11201</v>
+        <v>11101</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.02</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +638,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11101</v>
+        <v>11102</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1.09</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-11.1</v>
+        <v>-4.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.52</v>
+        <v>75.18</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.63</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.09</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.46</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.99</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.91</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.43</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.24</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-3.78</v>
+        <v>-37.84</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-4.36</v>
+        <v>-43.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:30</t>
+    <t xml:space="preserve">2026-10-04 08:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:17</t>
+    <t xml:space="preserve">2026-10-05 08:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
